--- a/data/trans_camb/IMC_inf_MED_R3-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R3-Dificultad-trans_camb.xlsx
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-14.51617284891537</v>
+        <v>-12.84690778306313</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-4.296416734509006</v>
+        <v>-3.024708442161067</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-9.970721981302535</v>
+        <v>-10.50644050717935</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-9.00713892306349</v>
+        <v>-7.263647817570748</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-12.17680458441574</v>
+        <v>-11.5694928118111</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-5.496167734656321</v>
+        <v>-4.194174174989645</v>
       </c>
     </row>
     <row r="5">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-22.51766317639672</v>
+        <v>-19.889750335175</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-18.44839550712328</v>
+        <v>-16.39721984260801</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-16.71780880494439</v>
+        <v>-16.32384715729581</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-19.62773613539607</v>
+        <v>-18.18574956084008</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-17.4623033245488</v>
+        <v>-16.36517233082654</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-15.36915814416165</v>
+        <v>-13.36351728627045</v>
       </c>
     </row>
     <row r="6">
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>-7.167973049006399</v>
+        <v>-6.042039927571609</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>11.69316883945806</v>
+        <v>11.05774163786243</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>-3.102597834946666</v>
+        <v>-4.149332609720255</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>5.576382641917532</v>
+        <v>5.536124106189493</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-7.197409956803316</v>
+        <v>-7.058434276122266</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>5.261004431816896</v>
+        <v>5.943856473160837</v>
       </c>
     </row>
     <row r="7">
@@ -679,22 +679,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-0.3907343860602062</v>
+        <v>-0.3683361109455218</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.1156474073772556</v>
+        <v>-0.08672198502105655</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-0.3943340068866141</v>
+        <v>-0.438075175548357</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.3562250746512152</v>
+        <v>-0.3028641137433157</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.388403599726483</v>
+        <v>-0.390933617599218</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.1753112910732886</v>
+        <v>-0.1417213104965183</v>
       </c>
     </row>
     <row r="8">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.5419947675687458</v>
+        <v>-0.5080007156856619</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-0.4630744838957048</v>
+        <v>-0.4438266545014754</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0.5785153043389401</v>
+        <v>-0.6090526902505714</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.7148637984551409</v>
+        <v>-0.6984668216265225</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.5117956762461706</v>
+        <v>-0.5092419246914032</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.4685702917121324</v>
+        <v>-0.4356146501163969</v>
       </c>
     </row>
     <row r="9">
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>-0.206958737924265</v>
+        <v>-0.1869139888567791</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.354985781321061</v>
+        <v>0.3413271105443514</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>-0.1368149577825224</v>
+        <v>-0.2119893512578822</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.264194281081149</v>
+        <v>0.2572378706190602</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.2404650124961664</v>
+        <v>-0.2605938739002522</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.194458285849498</v>
+        <v>0.2109815652894621</v>
       </c>
     </row>
     <row r="10">
@@ -761,22 +761,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-3.249658923518175</v>
+        <v>-2.485238057660319</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-9.496485738592245</v>
+        <v>-8.493149910422417</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-10.42957334217623</v>
+        <v>-10.39626190335218</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-10.69398078345337</v>
+        <v>-9.544009003091759</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-6.798693780361961</v>
+        <v>-6.388851220169989</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-9.870221290433733</v>
+        <v>-8.866164374399208</v>
       </c>
     </row>
     <row r="11">
@@ -787,22 +787,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-11.03410340433771</v>
+        <v>-9.761196980777575</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-17.37874395255038</v>
+        <v>-15.55653866294797</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-17.78886796240941</v>
+        <v>-16.45679783247328</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-19.01370082127154</v>
+        <v>-17.0843838908878</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-11.77742120161437</v>
+        <v>-11.23970113025409</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-15.64568843275452</v>
+        <v>-14.18011443136181</v>
       </c>
     </row>
     <row r="12">
@@ -813,22 +813,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>4.142798129429994</v>
+        <v>4.883400813841233</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-0.3202693835348815</v>
+        <v>0.1401498283762326</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-3.398429495529042</v>
+        <v>-3.50942667431055</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-1.335252458455242</v>
+        <v>-0.3125442587162334</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-1.128684163858889</v>
+        <v>-1.334249280114157</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-3.494543129564032</v>
+        <v>-2.679917198530196</v>
       </c>
     </row>
     <row r="13">
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>-0.1310710031627623</v>
+        <v>-0.107406326317693</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.3830290936904194</v>
+        <v>-0.3670545877615869</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>-0.455892740122988</v>
+        <v>-0.4708151160349592</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.4674503972732843</v>
+        <v>-0.4322191714678203</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.2849335601554369</v>
+        <v>-0.2825121688029424</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.4136614153631648</v>
+        <v>-0.3920578582996425</v>
       </c>
     </row>
     <row r="14">
@@ -865,22 +865,22 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-0.3832986810535843</v>
+        <v>-0.3630146384559029</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-0.6270332672122615</v>
+        <v>-0.5957769314194102</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-0.6705897793709069</v>
+        <v>-0.6638733584195389</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.7239750077667947</v>
+        <v>-0.7083868430346352</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.4408163642142321</v>
+        <v>-0.4425539159903836</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.6048376378131833</v>
+        <v>-0.5628248054328477</v>
       </c>
     </row>
     <row r="15">
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0.1950118337118269</v>
+        <v>0.2555079956417129</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>-0.01243416846314012</v>
+        <v>0.02993379842396538</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>-0.1729605027030446</v>
+        <v>-0.1809616479281283</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.02430124732025216</v>
+        <v>0.02269159394501754</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.04977389049642779</v>
+        <v>-0.0571410382860436</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.1372638432833331</v>
+        <v>-0.1119192807545876</v>
       </c>
     </row>
     <row r="16">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.08024939350373128</v>
+        <v>2.107311626226602</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>3.184761510633929</v>
+        <v>5.385715789048994</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-1.576241371023557</v>
+        <v>-1.745876030626375</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-8.970765930747413</v>
+        <v>-8.01948029242519</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.7412024788179677</v>
+        <v>0.1930052053068787</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-2.082642261842191</v>
+        <v>-0.510266373473367</v>
       </c>
     </row>
     <row r="17">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-7.887069981481752</v>
+        <v>-4.473911836881188</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-6.587761751954443</v>
+        <v>-2.496678640701298</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-10.46712249511712</v>
+        <v>-8.919759469670636</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-16.18489954483928</v>
+        <v>-14.54706465888363</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-6.488744830702893</v>
+        <v>-4.654102575944704</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-8.227277380463125</v>
+        <v>-6.530268945633083</v>
       </c>
     </row>
     <row r="18">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>9.297819371015303</v>
+        <v>9.448873376723164</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>12.52661706275568</v>
+        <v>13.70742822781121</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>6.727749977135867</v>
+        <v>4.84174690759319</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.7220462192995164</v>
+        <v>-0.335269190590248</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>5.303467491270169</v>
+        <v>4.833055866584372</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>4.077233842905459</v>
+        <v>4.538596797976322</v>
       </c>
     </row>
     <row r="19">
@@ -999,22 +999,22 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.004465554081807514</v>
+        <v>0.1438062905262308</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.1772190934095166</v>
+        <v>0.3675297947454143</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-0.08999668636467115</v>
+        <v>-0.1076405007307951</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.512192626562069</v>
+        <v>-0.4944342319469782</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.04177735763546936</v>
+        <v>0.01250990939405498</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.1173866697511304</v>
+        <v>-0.03307364736010741</v>
       </c>
     </row>
     <row r="20">
@@ -1025,22 +1025,22 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>-0.3494303633875613</v>
+        <v>-0.2695103289082743</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-0.298191742682049</v>
+        <v>-0.1332609043607046</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-0.4647796165991946</v>
+        <v>-0.4504962744235924</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.7739775024897483</v>
+        <v>-0.7396301409687666</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.3321609136908279</v>
+        <v>-0.2650835342768246</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.4071692144487165</v>
+        <v>-0.3768602820793155</v>
       </c>
     </row>
     <row r="21">
@@ -1051,22 +1051,22 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>0.6704821431300452</v>
+        <v>0.8144073176526341</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.9441899641430119</v>
+        <v>1.285597105381053</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.5155687902790215</v>
+        <v>0.3926551728022332</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>-0.02493605750311901</v>
+        <v>0.03645375128283598</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.3646238316223707</v>
+        <v>0.3719537885897396</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.2672538352851223</v>
+        <v>0.3504430599353996</v>
       </c>
     </row>
     <row r="22">
@@ -1081,22 +1081,22 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-4.955486586668284</v>
+        <v>-7.72857619915891</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>-11.21952103266332</v>
+        <v>-10.90932566761909</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-8.362784236714511</v>
+        <v>-9.478040912129657</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-6.908438037858013</v>
+        <v>-8.72882171415948</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-6.210384038479861</v>
+        <v>-8.232923405964248</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-9.109472048149131</v>
+        <v>-9.900349209158163</v>
       </c>
     </row>
     <row r="23">
@@ -1107,22 +1107,22 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-18.14120907516192</v>
+        <v>-18.84139551706788</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-22.72345553576674</v>
+        <v>-21.76509070972035</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-18.50980883344371</v>
+        <v>-19.52025061043862</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-17.24348814359888</v>
+        <v>-18.69611272509698</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-14.46736213450732</v>
+        <v>-15.92745379034443</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-16.55744071023528</v>
+        <v>-18.23556205123039</v>
       </c>
     </row>
     <row r="24">
@@ -1133,22 +1133,22 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>7.558503856355268</v>
+        <v>2.769990178767708</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1.801552318120711</v>
+        <v>0.2621840792748663</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>2.818788717904282</v>
+        <v>0.2064910020319612</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>2.628320656532037</v>
+        <v>1.067021674799008</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>2.03941720432119</v>
+        <v>-0.4267447158043236</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-0.6724345842584826</v>
+        <v>-2.125795035675635</v>
       </c>
     </row>
     <row r="25">
@@ -1159,22 +1159,22 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>-0.1832631136497567</v>
+        <v>-0.2955252991273609</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>-0.4149187616885882</v>
+        <v>-0.4171507982999236</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>-0.4687666569724938</v>
+        <v>-0.4684938684024371</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.3872448830726504</v>
+        <v>-0.4314604135363354</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.2743530705635899</v>
+        <v>-0.3520073733673914</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.4024246507361967</v>
+        <v>-0.4232999323194273</v>
       </c>
     </row>
     <row r="26">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>-0.5550110196571536</v>
+        <v>-0.5798556314027233</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>-0.6867293341740028</v>
+        <v>-0.6794971845258129</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-0.77656571861768</v>
+        <v>-0.7502265650945037</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-0.7259799316837857</v>
+        <v>-0.6965649626017709</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.5384300506028131</v>
+        <v>-0.5754550288495428</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.6126163905937226</v>
+        <v>-0.6408687327157773</v>
       </c>
     </row>
     <row r="27">
@@ -1211,22 +1211,22 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0.3556030502084783</v>
+        <v>0.1894530573900687</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.09773470052307724</v>
+        <v>0.03817283831760344</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.3278978103481875</v>
+        <v>0.08367770217230101</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.2580982890932462</v>
+        <v>0.1539416518913642</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.1206749720967606</v>
+        <v>-0.006081648138064792</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.01635023497877904</v>
+        <v>-0.0995326501998508</v>
       </c>
     </row>
     <row r="28">
@@ -1241,22 +1241,22 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>-6.574740562196363</v>
+        <v>-5.628345111792921</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>-7.904395832664712</v>
+        <v>-6.573113180995013</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-7.932482436919361</v>
+        <v>-8.304697704715217</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-10.68513515657753</v>
+        <v>-9.758618197673901</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-7.176836418699975</v>
+        <v>-6.851084376741243</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-8.794573268666211</v>
+        <v>-7.731948736335781</v>
       </c>
     </row>
     <row r="29">
@@ -1267,22 +1267,22 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>-11.17227212966228</v>
+        <v>-9.424378168308547</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>-13.0788283410985</v>
+        <v>-11.4698121310585</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-11.83653812451507</v>
+        <v>-11.93092818045535</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-15.5233668976246</v>
+        <v>-13.68583536417412</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-9.961653830696191</v>
+        <v>-9.506976917126773</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-12.15672486945898</v>
+        <v>-11.19452604621433</v>
       </c>
     </row>
     <row r="30">
@@ -1293,22 +1293,22 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>-2.273291575845482</v>
+        <v>-1.519211833624593</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>-2.521803967894248</v>
+        <v>-1.849280040303107</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-4.346166659925272</v>
+        <v>-4.704963103908676</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-6.260900224831245</v>
+        <v>-5.466138224233587</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-4.121544905127951</v>
+        <v>-4.360325799069741</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>-5.027194965868655</v>
+        <v>-4.573263066316448</v>
       </c>
     </row>
     <row r="31">
@@ -1319,22 +1319,22 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>-0.2358538828084991</v>
+        <v>-0.218647211404732</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>-0.2835522452564285</v>
+        <v>-0.255349101507819</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>-0.3622371954458254</v>
+        <v>-0.3920201905480968</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-0.4879372154754362</v>
+        <v>-0.4606519708918693</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.2876598240980061</v>
+        <v>-0.2913295912150862</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.3525014716637235</v>
+        <v>-0.3287867059848038</v>
       </c>
     </row>
     <row r="32">
@@ -1345,22 +1345,22 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>-0.3727336799792862</v>
+        <v>-0.3412273920444677</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>-0.4346921462342426</v>
+        <v>-0.4241223568166254</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-0.495373611376248</v>
+        <v>-0.5152943071899796</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-0.6452338680793247</v>
+        <v>-0.6016613342196445</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.3800447660264966</v>
+        <v>-0.3796036765862728</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.4657512250846947</v>
+        <v>-0.4496212652374292</v>
       </c>
     </row>
     <row r="33">
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>-0.08737745099573867</v>
+        <v>-0.06540691071810201</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>-0.09593222588321092</v>
+        <v>-0.06838572371861386</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>-0.214123455158205</v>
+        <v>-0.2391173751758583</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-0.3051769322718925</v>
+        <v>-0.2594917890574195</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.1715831707107707</v>
+        <v>-0.1959732297991427</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.2084282868886631</v>
+        <v>-0.1982152743985499</v>
       </c>
     </row>
     <row r="34">
